--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -842,22 +834,22 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -890,12 +882,12 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -953,7 +945,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -963,7 +955,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1006,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/16</t>
         </is>
       </c>
     </row>
@@ -1064,22 +1056,22 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1112,12 +1104,12 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1167,7 +1159,1339 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1283,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1505,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1727,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2301,7 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2325,12 +2349,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2404,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2465,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2485,13 +2509,913 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr"/>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>—/16</t>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1244,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1283,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1322,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1355,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1433,32 +1449,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1466,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1490,17 +1510,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1510,13 +1530,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1616,7 +1640,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1655,32 +1679,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1688,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1712,17 +1740,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1732,13 +1760,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1766,32 +1798,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -1799,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1823,33 +1859,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1917,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1910,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1934,33 +1978,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1988,32 +2036,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -2021,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2045,33 +2097,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2099,32 +2155,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2132,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2156,17 +2216,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2176,13 +2236,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2274,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2243,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2267,33 +2335,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2321,32 +2393,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -2354,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2378,17 +2454,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2398,13 +2474,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2432,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2465,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2489,17 +2573,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2509,17 +2593,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2619,7 +2703,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2691,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2845,7 +2929,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2860,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2921,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3032,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3071,7 +3155,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3100,7 +3184,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3143,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3157,7 +3241,7 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3201,22 +3285,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3249,12 +3333,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3298,13 +3382,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3400,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3322,7 +3410,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3360,12 +3448,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3379,41 +3467,1183 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2522,24 +2522,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2631,32 +2631,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,17 +2692,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2708,13 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2742,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2775,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2799,37 +2811,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2944,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3056,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3116,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3227,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3338,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3392,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3568,7 +3580,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3607,7 +3619,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3683,7 +3695,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,7 +3810,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,7 +3921,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3963,7 +3975,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4036,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4151,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4193,7 +4205,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4266,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4381,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4413,13 +4425,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4496,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4534,7 +4550,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4542,22 +4558,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4590,12 +4606,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4609,43 +4625,384 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr"/>
-      <c r="AC36" s="2" t="inlineStr">
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1645,13 +1645,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,22 +1759,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1889,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,17 +2121,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2956,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3128,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3239,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3350,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3404,7 +3408,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3432,32 +3436,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3465,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3489,37 +3497,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3634,7 +3642,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3662,32 +3670,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3695,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3719,37 +3731,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3777,32 +3789,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3810,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3834,17 +3850,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3854,13 +3870,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3960,7 +3980,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3975,7 +3995,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4003,32 +4023,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -4036,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4060,17 +4084,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4080,17 +4104,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4205,7 +4229,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4290,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4320,7 +4344,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4435,7 +4459,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4520,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4550,7 +4574,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4635,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4665,7 +4689,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4750,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,7 +4861,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4895,22 +4919,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4943,12 +4967,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4962,47 +4986,392 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
+      <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>94.0</t>
         </is>
       </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>8/18</t>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,18 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1774,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,17 +2120,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2250,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2369,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,17 +2834,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3132,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3171,18 +3175,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3408,7 +3416,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,22 +3520,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3642,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3761,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3908,32 +3916,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -3941,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3965,17 +3977,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3985,17 +3997,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4033,24 +4045,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4060,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4099,17 +4111,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4142,32 +4154,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4175,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4199,37 +4215,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4329,7 +4345,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4344,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4372,32 +4388,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -4405,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4429,17 +4449,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4449,17 +4469,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4487,32 +4507,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4520,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4544,37 +4568,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4602,32 +4626,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4635,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4659,32 +4687,32 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4717,32 +4745,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -4750,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4774,33 +4806,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4939,32 +4975,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4972,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4996,37 +5036,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5127,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5141,7 +5181,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5242,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5256,7 +5296,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5264,22 +5304,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5317,7 +5357,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5331,47 +5371,852 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,22 +3635,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,22 +3992,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4230,22 +4230,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4985,24 +4985,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5094,32 +5094,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5127,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5151,37 +5155,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5324,32 +5328,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5357,7 +5365,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5381,32 +5389,32 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5439,32 +5447,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5472,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5496,37 +5508,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5554,32 +5566,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5587,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5611,32 +5627,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5669,32 +5685,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5702,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5726,37 +5746,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5871,7 +5891,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5986,7 +6006,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6067,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6096,12 +6116,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6182,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6211,10 +6231,585 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>3/18</t>
         </is>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3175,17 +3175,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,22 +3520,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,22 +4583,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,22 +4702,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4821,17 +4821,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5051,22 +5051,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5576,24 +5576,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5804,32 +5804,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5837,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5861,37 +5865,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5919,32 +5923,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5952,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5976,37 +5984,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6034,32 +6042,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -6067,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6091,32 +6103,32 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6149,32 +6161,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6182,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6206,37 +6222,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6264,32 +6280,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6297,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6321,17 +6341,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6341,17 +6361,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,7 +6547,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6581,7 +6601,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6662,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6691,7 +6711,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6757,7 +6777,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6806,12 +6826,587 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,14 +2239,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,22 +3992,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4350,17 +4350,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5404,17 +5404,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5523,22 +5523,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5647,17 +5647,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6052,24 +6052,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6399,32 +6399,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6432,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6456,32 +6460,32 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6514,32 +6518,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6547,7 +6555,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6571,37 +6579,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6637,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6662,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6686,17 +6698,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6706,17 +6718,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6744,32 +6756,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6777,7 +6793,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6801,17 +6817,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6821,12 +6837,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6892,7 +6908,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7007,7 +7023,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7061,7 +7077,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7138,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7171,12 +7187,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7253,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,7 +7368,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7410,6 +7426,466 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,14 +2477,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>89.0</t>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,14 +2834,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3180,17 +3180,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4230,17 +4230,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,22 +4583,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,14 +4702,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4864,12 +4864,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程39%处后消失；随后反向物理轨迹由seq26推进至seq34，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4897,18 +4897,30 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
           <t>10:50</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq17映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4936,7 +4948,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5012,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,12 +5068,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5131,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5246,7 +5258,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5300,7 +5312,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5484,7 +5496,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5533,7 +5545,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5603,7 +5615,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5642,7 +5654,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5652,12 +5664,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5761,17 +5773,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5841,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5880,22 +5892,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5999,14 +6011,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -6014,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,17 +6135,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6242,12 +6254,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6317,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6436,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,24 +6540,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6555,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6604,7 +6616,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6647,19 +6659,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6674,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6713,7 +6725,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6723,12 +6735,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6766,12 +6778,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6793,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6832,17 +6844,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6875,32 +6887,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6908,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6932,37 +6948,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6990,32 +7006,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7023,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7047,29 +7067,29 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -7077,7 +7097,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7105,32 +7125,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -7138,7 +7162,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7162,17 +7186,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7182,17 +7206,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7335,32 +7359,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7368,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7392,17 +7420,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7412,12 +7440,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7483,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,7 +7626,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7762,7 +7790,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7775,22 +7803,22 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7823,12 +7851,12 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7867,22 +7895,1053 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
+      <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="AC63" s="2" t="inlineStr">
+      <c r="AC64" s="2" t="inlineStr">
         <is>
           <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,22 +3992,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,22 +4345,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq23推进至seq37，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5266,10 +5266,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq15（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq15映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5297,7 +5309,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5312,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5416,17 +5428,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5496,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5535,22 +5547,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5654,22 +5666,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5853,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5907,7 +5919,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6026,7 +6038,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6130,7 +6142,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6210,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6249,7 +6261,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6329,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6368,7 +6380,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6448,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6487,17 +6499,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6567,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6606,22 +6618,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6725,22 +6737,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6924,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6978,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7097,7 +7109,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7201,7 +7213,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7244,32 +7256,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7277,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7301,37 +7317,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7397,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7396,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,7 +7451,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7511,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7550,7 +7566,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7593,32 +7609,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7626,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7650,32 +7670,32 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7708,32 +7728,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7741,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7765,37 +7789,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7823,32 +7847,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7856,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7880,32 +7908,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7938,32 +7966,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7971,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7995,37 +8027,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8053,32 +8085,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8086,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8110,37 +8146,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8316,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8370,7 +8406,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8546,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8657,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8711,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8826,7 +8862,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8834,22 +8870,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8882,12 +8918,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8926,22 +8962,1172 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>84.4</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
         <is>
           <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,18 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,17 +1533,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,12 +2005,12 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2492,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3064,18 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3362,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3416,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,17 +3528,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3596,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3715,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3754,22 +3762,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3873,7 +3881,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3953,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4007,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4191,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4230,12 +4238,12 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4306,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4355,12 +4363,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4464,22 +4472,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,22 +4591,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,22 +4710,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4897,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,18 +4956,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,17 +5075,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5143,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5258,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5309,22 +5321,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5508,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5562,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5676,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,12 +5797,12 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5865,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,22 +5916,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6023,22 +6035,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6222,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6261,17 +6273,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6341,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6460,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6579,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6633,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6747,12 +6759,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,12 +6868,12 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6936,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,22 +6987,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7094,22 +7106,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7293,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,17 +7463,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7527,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7646,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7765,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7819,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7938,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8057,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8095,12 +8107,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
@@ -8122,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8171,12 +8183,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8276,7 +8288,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8352,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8391,7 +8403,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8406,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8434,32 +8446,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8467,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8491,27 +8507,27 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8549,32 +8565,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8582,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8606,33 +8626,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB69" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8660,32 +8684,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -8693,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8717,37 +8745,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8775,32 +8803,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8808,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8832,37 +8864,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8890,32 +8922,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8923,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8947,37 +8983,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9005,32 +9041,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9038,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9062,37 +9102,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9235,32 +9275,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9268,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9292,32 +9336,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9383,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9437,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9613,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9728,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9782,7 +9826,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9897,7 +9941,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9958,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10012,7 +10056,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10122,12 +10166,1047 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
           <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,17 +3409,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3648,17 +3648,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,22 +4000,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,22 +4119,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4358,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4829,22 +4829,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5199,17 +5199,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,22 +5559,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,17 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6154,22 +6154,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,17 +6397,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6511,22 +6511,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,22 +6630,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7225,22 +7225,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,22 +7344,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,22 +7697,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7816,22 +7816,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,17 +7935,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,22 +8054,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9160,32 +9160,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -9193,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9217,37 +9221,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9285,24 +9289,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9312,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9361,7 +9365,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9394,32 +9398,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9427,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,37 +9459,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9509,32 +9517,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9542,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9566,17 +9578,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9586,17 +9598,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9624,32 +9636,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9657,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,37 +9697,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9739,32 +9755,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9772,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9796,37 +9816,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9854,32 +9874,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9887,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,37 +9935,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9969,32 +9993,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10002,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,32 +10054,32 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10084,32 +10112,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10117,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10141,17 +10173,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10161,17 +10193,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10347,7 +10379,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10386,7 +10418,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10401,7 +10433,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10494,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10516,7 +10548,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10616,7 +10648,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10631,7 +10663,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10746,7 +10778,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10839,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10861,7 +10893,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10954,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10976,7 +11008,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11037,7 +11069,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11091,7 +11123,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11184,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11201,12 +11233,932 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
           <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>95.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,17 +3533,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4363,12 +4363,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,22 +4472,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6040,17 +6040,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6873,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,17 +7468,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7945,12 +7945,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8408,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,17 +8527,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8760,22 +8760,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,17 +9122,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,17 +9360,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10003,24 +10003,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10079,12 +10079,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10122,24 +10122,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10346,32 +10346,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10379,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10403,17 +10407,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10423,17 +10427,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10465,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10494,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10518,17 +10526,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10538,17 +10546,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10576,32 +10584,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10609,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10633,17 +10645,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10653,17 +10665,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10691,32 +10703,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -10724,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10748,37 +10764,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10839,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10893,7 +10909,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10921,32 +10937,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10954,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10978,17 +10998,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10998,17 +11018,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11089,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11108,7 +11128,7 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11123,7 +11143,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11151,32 +11171,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11184,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11208,17 +11232,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11228,17 +11252,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11323,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11353,7 +11377,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11468,7 +11492,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11553,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11568,7 +11592,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11583,7 +11607,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11668,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11698,7 +11722,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11813,7 +11837,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11898,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11918,17 +11942,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11989,7 +12013,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12038,12 +12062,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12128,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12148,17 +12172,477 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>4/18</t>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,22 +3409,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,17 +3767,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,17 +4124,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4834,17 +4834,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,17 +7230,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7702,17 +7702,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,22 +7935,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8408,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,17 +9003,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,17 +9241,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,17 +9717,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9836,17 +9836,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,17 +9955,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10069,22 +10069,22 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10303,17 +10303,17 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10665,17 +10665,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -11056,32 +11056,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11089,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11113,17 +11117,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11133,17 +11137,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11290,32 +11294,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -11323,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11347,17 +11355,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11367,17 +11375,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11405,32 +11413,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11438,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11462,17 +11474,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11482,17 +11494,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11635,32 +11647,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11668,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11692,17 +11708,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11712,17 +11728,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11750,32 +11766,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11783,7 +11803,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11807,17 +11827,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11827,17 +11847,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11865,32 +11885,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11898,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11922,17 +11946,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11942,17 +11966,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11980,32 +12004,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12013,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12037,37 +12065,37 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12095,32 +12123,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12128,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12152,17 +12184,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12172,17 +12204,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12210,32 +12242,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12243,7 +12279,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12267,32 +12303,32 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12358,7 +12394,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12402,17 +12438,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12473,7 +12509,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12512,7 +12548,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12588,7 +12624,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12646,6 +12682,351 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,17 +3767,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4477,17 +4477,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,17 +7349,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,17 +9003,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,17 +9479,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10784,17 +10784,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11137,17 +11137,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,17 +11609,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12133,12 +12133,12 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12252,24 +12252,24 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12361,32 +12361,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12394,7 +12398,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12418,17 +12422,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12438,17 +12442,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12476,32 +12480,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -12509,7 +12517,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12533,17 +12541,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12553,17 +12561,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12591,32 +12599,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -12624,7 +12636,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12648,17 +12660,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12668,17 +12680,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12751,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12793,7 +12805,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12866,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12903,7 +12915,7 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
@@ -12969,7 +12981,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13013,17 +13025,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-10-浦东78路.xlsx
+++ b/data/export/2026-10-10-浦东78路.xlsx
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,17 +7940,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,17 +10074,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,12 +10308,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12085,17 +12085,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12718,32 +12718,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12751,7 +12755,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12775,17 +12779,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12795,17 +12799,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12833,32 +12837,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12866,7 +12874,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12890,17 +12898,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12910,12 +12918,12 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
@@ -12981,7 +12989,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
